--- a/phan-cong-cong-viec.xlsx
+++ b/phan-cong-cong-viec.xlsx
@@ -1393,7 +1393,7 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>231 quốc gia · 25.754 cạnh (năm 2024) · mật độ 0,485 · top 1% cạnh chiếm 60,6% giá trị</t>
+          <t>231 quốc gia · 27.535 cạnh (năm 2023) · mật độ 0,518 · top 1% cạnh chiếm 61,2% giá trị — 2023 là năm đủ dữ liệu gần nhất, bản Atlas 2024 còn tạm (thiếu 1.781 cặp nước)</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quyết định ngưỡng lọc cạnh và biện minh bằng số liệu. Đã chốt: ngưỡng tương đối 0,046% tổng xuất khẩu thế giới mỗi năm, cộng giữ top-3 luồng vào/ra cho mỗi nước ASEAN → 408 cạnh, 68,1% giá trị (2024), ASEAN đủ 10/10 ở mọi năm.</t>
+          <t>Quyết định ngưỡng lọc cạnh và biện minh bằng số liệu. Đã chốt: ngưỡng tương đối 0,046% tổng xuất khẩu thế giới mỗi năm, cộng giữ top-3 luồng vào/ra cho mỗi nước ASEAN → 416 cạnh, 67,8% giá trị (2023), ASEAN đủ 10/10 ở mọi năm.</t>
         </is>
       </c>
       <c r="D14" s="26" t="inlineStr">

--- a/phan-cong-cong-viec.xlsx
+++ b/phan-cong-cong-viec.xlsx
@@ -1753,7 +1753,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Chờ review</t>
         </is>
       </c>
     </row>

--- a/phan-cong-cong-viec.xlsx
+++ b/phan-cong-cong-viec.xlsx
@@ -1873,7 +1873,7 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Chờ review</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Bảng màu vẫn phân biệt được với người mù màu đỏ–xanh lá.</t>
+          <t>Bảng màu vẫn phân biệt được với người mù màu đỏ–xanh lá. Đo bằng src/check_palette.py (ma trận Machado 2009 + CIEDE2000): cặp gần nhau nhất ΔE = 13,3 với người mù đỏ và 12,3 với người mù lục, ngưỡng đặt ra là 10.</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đạt</t>
         </is>
       </c>
     </row>

--- a/phan-cong-cong-viec.xlsx
+++ b/phan-cong-cong-viec.xlsx
@@ -1538,7 +1538,7 @@
       <c r="D15" s="6" t="inlineStr">
         <is>
           <t>· Sankey luồng thương mại
-· Small multiples 1995→2024
+· Small multiples 1995→2023
 · Streamgraph cơ cấu ngành
 · Báo cáo/dashboard hoàn chỉnh
 · Slide thuyết trình</t>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Chờ review</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Chờ review</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Chờ review</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>2 treemap (1995 và 2024) dùng chung bảng màu</t>
+          <t>2 treemap (1995 và 2023) dùng chung bảng màu</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Chờ review</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Chờ review</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Chờ review</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Small multiples theo thời gian: vị trí của Việt Nam trong mạng lưới qua các mốc 1995, 2005, 2015, 2024.</t>
+          <t>Small multiples theo thời gian: vị trí của Việt Nam trong mạng lưới qua các mốc 1995, 2005, 2015, 2023.</t>
         </is>
       </c>
       <c r="D24" s="25" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Streamgraph cơ cấu ngành xuất khẩu Việt Nam giai đoạn 1995–2024 theo 10 ngành cấp 1.</t>
+          <t>Streamgraph cơ cấu ngành xuất khẩu Việt Nam giai đoạn 1995–2023 theo 10 ngành cấp 1.</t>
         </is>
       </c>
       <c r="D25" s="25" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đạt</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>File dữ liệu thô không bị commit. .gitignore đã loại .csv lớn.</t>
+          <t>File dữ liệu thô không bị commit. .gitignore đã loại .csv lớn. Da kiem 20/10: khong file tho nao duoc theo doi trong HEAD, file lon nhat la data/atlas/product_hs92.csv 837 KB (file tra cuu, .gitignore co ngoai le rieng). LUU Y: cc_year.csv 27 MB van nam trong LICH SU do PR #3 merge thuong thay vi squash - cay lam viec sach, .git thi 15 MB.</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đạt</t>
         </is>
       </c>
     </row>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đạt</t>
         </is>
       </c>
     </row>

--- a/phan-cong-cong-viec.xlsx
+++ b/phan-cong-cong-viec.xlsx
@@ -2153,7 +2153,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Chờ review</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Chờ review</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Chờ review</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Chờ review</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>

--- a/phan-cong-cong-viec.xlsx
+++ b/phan-cong-cong-viec.xlsx
@@ -2433,7 +2433,7 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>

--- a/phan-cong-cong-viec.xlsx
+++ b/phan-cong-cong-viec.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22188" windowHeight="9000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tổng quan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Phân công chi tiết" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Hợp đồng dữ liệu" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Tiến độ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Checklist nộp bài" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tổng quan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phân công chi tiết" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hợp đồng dữ liệu" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist nộp bài" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Phân công chi tiết'!$A$4:$H$34</definedName>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
     </row>
@@ -2913,10 +2913,11 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
-        </is>
-      </c>
-    </row>
+          <t>Đang làm</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="B36" s="27" t="inlineStr">
         <is>

--- a/phan-cong-cong-viec.xlsx
+++ b/phan-cong-cong-viec.xlsx
@@ -2060,7 +2060,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Bảng thống kê và biểu đồ phân bố bậc thang log-log</t>
+          <t>Bảng thống kê 30 năm + biểu đồ log-log phân bố bậc (output/degree_loglog_2023)</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>

--- a/phan-cong-cong-viec.xlsx
+++ b/phan-cong-cong-viec.xlsx
@@ -1675,6 +1675,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2301,7 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>1 node-link đọc được, khoảng 350 cạnh</t>
+          <t>Node-link 73 nút/416 cạnh, màu theo cụm Louvain (output/node_link_2023)</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -2313,7 +2314,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>

--- a/phan-cong-cong-viec.xlsx
+++ b/phan-cong-cong-viec.xlsx
@@ -1675,7 +1675,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2341,7 +2340,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>2 ma trận: thứ tự alphabet và thứ tự theo cụm</t>
+          <t>2 ma trận 73x73 cùng dữ liệu khác thứ tự: output/adjacency_alpha_2023.{html,png} và adjacency_cluster_2023.{html,png}, kèm năm đối chứng 1995 — src/make_adjacency_matrix.py</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -2354,7 +2353,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>

--- a/phan-cong-cong-viec.xlsx
+++ b/phan-cong-cong-viec.xlsx
@@ -1675,6 +1675,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2380,7 +2381,7 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>1 chord diagram</t>
+          <t>chord 8 khối, Việt Nam làm trọng tâm: output/chord_bloc_{1995,2023}.{html,png}</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -2393,7 +2394,7 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2917,6 +2918,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="B36" s="27" t="inlineStr">
         <is>

--- a/phan-cong-cong-viec.xlsx
+++ b/phan-cong-cong-viec.xlsx
@@ -1648,7 +1648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1675,7 +1675,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2461,7 +2460,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>1 Sankey 3 tầng</t>
+          <t>src/make_sankey.py → sankey_vietnam_{1995,2023}</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2474,7 +2473,7 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2500,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Lưới 4 khung</t>
+          <t>src/make_time_multiples.py → time_multiples_{xuat,nhap}</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -2514,7 +2513,7 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2540,7 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>1 streamgraph</t>
+          <t>src/make_streamgraph.py → stream_sectors_1995_2023</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -2554,7 +2553,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2580,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Toàn bộ biểu đồ đồng bộ</t>
+          <t>Khung point cho cả 10 script (R.xuat_png), 5 hình cũ bố cục lại</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -2594,7 +2593,7 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2660,7 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Báo cáo kiểm tra và bản sửa</t>
+          <t>src/check_readability.py — 5 phép kiểm, hiện ĐẠT</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -2674,7 +2673,7 @@
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2917,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="B36" s="27" t="inlineStr">
         <is>
@@ -2959,6 +2957,46 @@
       <c r="C39" t="inlineStr">
         <is>
           <t>riêng 42 giờ  +  phần chung 17 giờ  =  59 giờ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>T31</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>3. Trực quan hóa (Tuần 3–4)</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Mặt phẳng quyết định RCA × PCI — hình mang ĐỀ XUẤT (phát sinh, xem B18)</t>
+        </is>
+      </c>
+      <c r="D40" s="25" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>src/make_decision_plane.py → decision_plane_{2015,2023}</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>T04, T07</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Xong</t>
         </is>
       </c>
     </row>

--- a/phan-cong-cong-viec.xlsx
+++ b/phan-cong-cong-viec.xlsx
@@ -2700,12 +2700,12 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>2–3 trang</t>
+          <t>.report/final/02-phuong-phap-luan.md — 12 muc, 5.728 tu; moi con so kem lenh lay lai. Dai hon 2-3 trang du tinh: ban goc day du, ke hoach cat nam o dau file</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>T08, T10</t>
+          <t>T10 (T08 bo theo B9)</t>
         </is>
       </c>
       <c r="G29" s="4" t="n">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>

--- a/phan-cong-cong-viec.xlsx
+++ b/phan-cong-cong-viec.xlsx
@@ -2740,7 +2740,7 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>3–4 trang</t>
+          <t>.report/final/03-phat-hien.md - 9 muc theo mach lap luan. Phat hien moi A16: phep dem ban hang KHONG ben (47 nuoc roi danh sach chi mang 0,59% kim ngach; tren muc san 100 trieu USD thi so kenh TANG 13-&gt;83), phep ben la HHI: day 0,0662 (2013) -&gt; 0,1226 (2023). Sua A13 (dinh la 2002/208 nuoc, khong phai 2005/200), sua A4, sua tieu de hinh T20. Dai hon 3-4 trang du tinh: ban goc day du, ke hoach cat nam o dau file</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>

--- a/phan-cong-cong-viec.xlsx
+++ b/phan-cong-cong-viec.xlsx
@@ -1675,6 +1675,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2780,7 +2781,7 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Sản phẩm nộp hoàn chỉnh</t>
+          <t>10 file muc trong .report/final/ + src/build_report.py -&gt; output/bao-cao-cuoi.{md,html}. Bo cuc chot (B23): bon hoi Quy mo / Cau truc / Vi tri Viet Nam / Y nghia, kep giua Mo dau + Phuong phap luan va De xuat + Ket luan, roi Phu luc. Viet moi: Tom tat, Mo dau, Quy mo, De xuat, Ket luan. Phat hien A17: RCA khong tu di len (chi 45,4% trong 97 nhom tang 2015-&gt;2023, trung vi -0,0178); quy tac chon chay o 2007 chi ra dien tu truoc dot bung no. Do duoc: ~19 trang than + 3 trang phu luc, 14 hinh, 0 tham chieu cheo treo</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -2793,7 +2794,7 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>

--- a/phan-cong-cong-viec.xlsx
+++ b/phan-cong-cong-viec.xlsx
@@ -1675,7 +1675,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2821,7 +2820,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Bộ slide</t>
+          <t>output/slide-thuyet-trinh.html — 17 slide chính + 3 dự phòng, 16:9, lời dẫn kèm theo; dựng bằng src/build_slides.py, mọi số đo lại từ dữ liệu và đối chiếu với báo cáo cuối</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -2834,7 +2833,7 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>

--- a/phan-cong-cong-viec.xlsx
+++ b/phan-cong-cong-viec.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22188" windowHeight="9000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tổng quan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Phân công chi tiết" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Hợp đồng dữ liệu" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Tiến độ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Checklist nộp bài" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tổng quan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phân công chi tiết" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hợp đồng dữ liệu" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist nộp bài" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Phân công chi tiết'!$A$4:$H$34</definedName>
@@ -1675,7 +1675,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2021,7 +2020,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Bảng so sánh và một đoạn viết cho phần Phương pháp luận</t>
+          <t>src/compare_mirror.py → mirror_gap.csv: 2.093/2.093 luồng ≥ 1 tỷ USD trùng khít (A18); đoạn ở §2.2 .report/final/02-phuong-phap-luan.md. Đổi hướng vì BACI/Comtrade cùng gốc với Atlas (B9)</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -2034,7 +2033,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Xong</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2633,7 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2860,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Danh sách 10 câu hỏi kèm câu trả lời</t>
+          <t>docs/nhat-ky-cong-viec.md §4 — 10 câu kèm câu trả lời; còn diễn tập</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -2874,7 +2873,7 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
     </row>
@@ -2914,10 +2913,11 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
-        </is>
-      </c>
-    </row>
+          <t>Đang làm</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="B36" s="27" t="inlineStr">
         <is>
